--- a/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReply.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReply.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="359">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -442,6 +442,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -484,10 +494,17 @@
     <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>Communication.instantiatesCanonical</t>
@@ -503,6 +520,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -544,7 +564,14 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -570,16 +597,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -682,6 +699,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -760,6 +780,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -812,6 +835,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1106,7 +1132,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1499,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2437,19 +2469,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2461,7 +2493,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2475,10 +2507,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2504,16 +2536,16 @@
         <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2550,19 +2582,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2574,7 +2606,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2588,10 +2620,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2614,19 +2646,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2675,7 +2707,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2684,27 +2716,27 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2727,15 +2759,17 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2784,7 +2818,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2799,21 +2833,21 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2839,13 +2873,13 @@
         <v>101</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2895,7 +2929,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2910,25 +2944,25 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2947,16 +2981,16 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3006,7 +3040,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3015,27 +3049,27 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3058,13 +3092,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3115,7 +3149,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3136,15 +3170,15 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3173,7 +3207,7 @@
         <v>134</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>136</v>
@@ -3214,19 +3248,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3238,7 +3272,7 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
@@ -3247,15 +3281,15 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3278,16 +3312,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3337,7 +3371,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3346,7 +3380,7 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>99</v>
@@ -3363,10 +3397,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3392,13 +3426,13 @@
         <v>101</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3424,13 +3458,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3448,7 +3482,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3474,10 +3508,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3500,16 +3534,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3559,7 +3593,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3568,7 +3602,7 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
@@ -3580,15 +3614,15 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3611,16 +3645,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3670,7 +3704,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3696,14 +3730,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3722,15 +3756,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3779,7 +3815,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3788,27 +3824,27 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3831,15 +3867,17 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3888,7 +3926,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3897,10 +3935,10 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
@@ -3909,15 +3947,15 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3943,13 +3981,13 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3957,7 +3995,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>77</v>
@@ -3975,31 +4013,31 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>87</v>
@@ -4014,10 +4052,10 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4025,14 +4063,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4051,16 +4089,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4086,31 +4124,31 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4119,27 +4157,27 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4162,16 +4200,16 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4197,13 +4235,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4221,7 +4259,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4230,7 +4268,7 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -4239,18 +4277,18 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4276,20 +4314,20 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>77</v>
@@ -4310,13 +4348,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4334,7 +4372,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4352,7 +4390,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4360,10 +4398,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4386,15 +4424,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4419,13 +4459,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4443,7 +4483,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4452,7 +4492,7 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
@@ -4464,19 +4504,19 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4495,15 +4535,17 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4552,7 +4594,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4561,27 +4603,27 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4604,16 +4646,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4639,13 +4681,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4663,7 +4705,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4672,7 +4714,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4681,18 +4723,18 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4715,16 +4757,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4774,7 +4816,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4783,27 +4825,27 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4826,16 +4868,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4885,7 +4927,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4894,27 +4936,27 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4937,13 +4979,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4994,7 +5036,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5009,10 +5051,10 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5020,10 +5062,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5046,13 +5088,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5103,7 +5145,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5118,10 +5160,10 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5129,10 +5171,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5155,15 +5197,17 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5212,7 +5256,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5221,27 +5265,27 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5264,13 +5308,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5321,7 +5365,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5342,15 +5386,15 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5379,7 +5423,7 @@
         <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>136</v>
@@ -5420,19 +5464,19 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5444,7 +5488,7 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5453,15 +5497,15 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5484,16 +5528,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5543,7 +5587,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5552,7 +5596,7 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
@@ -5569,10 +5613,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5598,13 +5642,13 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5630,13 +5674,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5654,7 +5698,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5680,10 +5724,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5706,16 +5750,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5765,7 +5809,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5774,7 +5818,7 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
@@ -5786,15 +5830,15 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5817,16 +5861,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5876,7 +5920,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5902,10 +5946,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5928,15 +5972,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -5985,7 +6031,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -5994,27 +6040,27 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6037,13 +6083,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6094,7 +6140,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6115,15 +6161,15 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6152,7 +6198,7 @@
         <v>134</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>136</v>
@@ -6193,19 +6239,19 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6217,7 +6263,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6226,15 +6272,15 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6257,16 +6303,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6316,7 +6362,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6325,7 +6371,7 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
@@ -6342,10 +6388,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6371,13 +6417,13 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6403,13 +6449,13 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6427,7 +6473,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6453,10 +6499,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6479,16 +6525,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6538,7 +6584,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6547,7 +6593,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
@@ -6559,15 +6605,15 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6590,16 +6636,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6649,7 +6695,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6675,10 +6721,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6701,16 +6747,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6736,13 +6782,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6760,7 +6806,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6769,27 +6815,27 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6812,15 +6858,17 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -6869,7 +6917,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6878,27 +6926,27 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6921,13 +6969,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6978,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -6987,7 +7035,7 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -6999,15 +7047,15 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7030,13 +7078,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7087,7 +7135,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7108,15 +7156,15 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7145,7 +7193,7 @@
         <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>136</v>
@@ -7186,19 +7234,19 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7210,7 +7258,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7219,19 +7267,19 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7253,16 +7301,16 @@
         <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>136</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7311,7 +7359,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7323,7 +7371,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7337,10 +7385,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7363,13 +7411,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7420,7 +7468,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>87</v>
@@ -7429,7 +7477,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -7441,15 +7489,15 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7472,15 +7520,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7529,7 +7579,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7538,19 +7588,19 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
